--- a/backend/exports/仓库-车队映射导入模板.xlsx
+++ b/backend/exports/仓库-车队映射导入模板.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aosom\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gihub\logix\backend\exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA804BC3-0F1C-406E-BC34-1732D4F57916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5460FCA-C8D9-4D06-A630-78B3DC8AAF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="97">
   <si>
     <t>ID</t>
   </si>
@@ -308,6 +308,10 @@
   </si>
   <si>
     <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拖卡费</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -692,16 +696,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J56"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:K56"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="21.625" customWidth="1"/>
     <col min="4" max="4" width="17.25" customWidth="1"/>
     <col min="5" max="5" width="11.75" customWidth="1"/>
     <col min="6" max="6" width="46.625" customWidth="1"/>
+    <col min="7" max="7" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -721,19 +726,22 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
         <v>11</v>
       </c>
@@ -746,20 +754,23 @@
       <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>10</v>
+      <c r="G2">
+        <v>700</v>
       </c>
       <c r="H2" t="s">
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -772,11 +783,14 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="I3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G3">
+        <v>700</v>
+      </c>
+      <c r="J3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -789,11 +803,14 @@
       <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="I4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G4">
+        <v>700</v>
+      </c>
+      <c r="J4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
         <v>11</v>
       </c>
@@ -806,11 +823,14 @@
       <c r="F5" t="s">
         <v>14</v>
       </c>
-      <c r="I5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G5">
+        <v>700</v>
+      </c>
+      <c r="J5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
         <v>11</v>
       </c>
@@ -823,11 +843,14 @@
       <c r="F6" t="s">
         <v>13</v>
       </c>
-      <c r="I6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G6">
+        <v>700</v>
+      </c>
+      <c r="J6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -840,11 +863,14 @@
       <c r="F7" t="s">
         <v>14</v>
       </c>
-      <c r="I7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G7">
+        <v>700</v>
+      </c>
+      <c r="J7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B8" t="s">
         <v>18</v>
       </c>
@@ -857,11 +883,14 @@
       <c r="F8" t="s">
         <v>20</v>
       </c>
-      <c r="I8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G8">
+        <v>700</v>
+      </c>
+      <c r="J8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
         <v>18</v>
       </c>
@@ -874,11 +903,14 @@
       <c r="F9" t="s">
         <v>20</v>
       </c>
-      <c r="I9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G9">
+        <v>700</v>
+      </c>
+      <c r="J9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
         <v>18</v>
       </c>
@@ -891,11 +923,14 @@
       <c r="F10" t="s">
         <v>20</v>
       </c>
-      <c r="I10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G10">
+        <v>700</v>
+      </c>
+      <c r="J10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
         <v>18</v>
       </c>
@@ -908,11 +943,14 @@
       <c r="F11" t="s">
         <v>20</v>
       </c>
-      <c r="I11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G11">
+        <v>700</v>
+      </c>
+      <c r="J11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B12" t="s">
         <v>24</v>
       </c>
@@ -925,11 +963,14 @@
       <c r="F12" t="s">
         <v>26</v>
       </c>
-      <c r="I12" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G12">
+        <v>700</v>
+      </c>
+      <c r="J12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B13" t="s">
         <v>24</v>
       </c>
@@ -942,11 +983,14 @@
       <c r="F13" t="s">
         <v>26</v>
       </c>
-      <c r="I13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G13">
+        <v>700</v>
+      </c>
+      <c r="J13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B14" t="s">
         <v>24</v>
       </c>
@@ -959,11 +1003,14 @@
       <c r="F14" t="s">
         <v>26</v>
       </c>
-      <c r="I14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G14">
+        <v>700</v>
+      </c>
+      <c r="J14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B15" t="s">
         <v>24</v>
       </c>
@@ -976,11 +1023,14 @@
       <c r="F15" t="s">
         <v>26</v>
       </c>
-      <c r="I15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G15">
+        <v>700</v>
+      </c>
+      <c r="J15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B16" t="s">
         <v>30</v>
       </c>
@@ -993,11 +1043,14 @@
       <c r="F16" t="s">
         <v>32</v>
       </c>
-      <c r="I16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G16">
+        <v>700</v>
+      </c>
+      <c r="J16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B17" t="s">
         <v>30</v>
       </c>
@@ -1010,11 +1063,14 @@
       <c r="F17" t="s">
         <v>33</v>
       </c>
-      <c r="I17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G17">
+        <v>700</v>
+      </c>
+      <c r="J17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B18" t="s">
         <v>30</v>
       </c>
@@ -1027,11 +1083,14 @@
       <c r="F18" t="s">
         <v>34</v>
       </c>
-      <c r="I18" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G18">
+        <v>700</v>
+      </c>
+      <c r="J18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B19" t="s">
         <v>30</v>
       </c>
@@ -1044,11 +1103,14 @@
       <c r="F19" t="s">
         <v>35</v>
       </c>
-      <c r="I19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G19">
+        <v>700</v>
+      </c>
+      <c r="J19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B20" t="s">
         <v>30</v>
       </c>
@@ -1061,11 +1123,14 @@
       <c r="F20" t="s">
         <v>36</v>
       </c>
-      <c r="I20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="G20">
+        <v>700</v>
+      </c>
+      <c r="J20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B21" t="s">
         <v>30</v>
       </c>
@@ -1078,11 +1143,14 @@
       <c r="F21" t="s">
         <v>34</v>
       </c>
-      <c r="I21" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G21">
+        <v>700</v>
+      </c>
+      <c r="J21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B22" t="s">
         <v>30</v>
       </c>
@@ -1095,11 +1163,14 @@
       <c r="F22" t="s">
         <v>32</v>
       </c>
-      <c r="I22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G22">
+        <v>700</v>
+      </c>
+      <c r="J22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B23" t="s">
         <v>30</v>
       </c>
@@ -1112,11 +1183,14 @@
       <c r="F23" t="s">
         <v>33</v>
       </c>
-      <c r="I23" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G23">
+        <v>700</v>
+      </c>
+      <c r="J23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B24" t="s">
         <v>30</v>
       </c>
@@ -1129,11 +1203,14 @@
       <c r="F24" t="s">
         <v>35</v>
       </c>
-      <c r="I24" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G24">
+        <v>700</v>
+      </c>
+      <c r="J24" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B25" t="s">
         <v>30</v>
       </c>
@@ -1146,11 +1223,14 @@
       <c r="F25" t="s">
         <v>36</v>
       </c>
-      <c r="I25" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G25">
+        <v>700</v>
+      </c>
+      <c r="J25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B26" t="s">
         <v>30</v>
       </c>
@@ -1163,11 +1243,14 @@
       <c r="F26" t="s">
         <v>34</v>
       </c>
-      <c r="I26" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G26">
+        <v>700</v>
+      </c>
+      <c r="J26" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B27" t="s">
         <v>30</v>
       </c>
@@ -1180,11 +1263,14 @@
       <c r="F27" t="s">
         <v>32</v>
       </c>
-      <c r="I27" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G27">
+        <v>700</v>
+      </c>
+      <c r="J27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B28" t="s">
         <v>30</v>
       </c>
@@ -1197,11 +1283,14 @@
       <c r="F28" t="s">
         <v>33</v>
       </c>
-      <c r="I28" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G28">
+        <v>700</v>
+      </c>
+      <c r="J28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B29" t="s">
         <v>30</v>
       </c>
@@ -1214,11 +1303,14 @@
       <c r="F29" t="s">
         <v>35</v>
       </c>
-      <c r="I29" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G29">
+        <v>700</v>
+      </c>
+      <c r="J29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B30" t="s">
         <v>30</v>
       </c>
@@ -1231,11 +1323,14 @@
       <c r="F30" t="s">
         <v>36</v>
       </c>
-      <c r="I30" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G30">
+        <v>700</v>
+      </c>
+      <c r="J30" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B31" t="s">
         <v>18</v>
       </c>
@@ -1248,11 +1343,14 @@
       <c r="F31" t="s">
         <v>20</v>
       </c>
-      <c r="I31" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G31">
+        <v>700</v>
+      </c>
+      <c r="J31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B32" t="s">
         <v>68</v>
       </c>
@@ -1265,11 +1363,14 @@
       <c r="F32" t="s">
         <v>49</v>
       </c>
-      <c r="I32" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G32">
+        <v>700</v>
+      </c>
+      <c r="J32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B33" t="s">
         <v>68</v>
       </c>
@@ -1282,11 +1383,14 @@
       <c r="F33" t="s">
         <v>47</v>
       </c>
-      <c r="I33" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G33">
+        <v>700</v>
+      </c>
+      <c r="J33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B34" t="s">
         <v>73</v>
       </c>
@@ -1299,11 +1403,14 @@
       <c r="F34" t="s">
         <v>48</v>
       </c>
-      <c r="I34" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G34">
+        <v>700</v>
+      </c>
+      <c r="J34" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B35" t="s">
         <v>73</v>
       </c>
@@ -1316,11 +1423,14 @@
       <c r="F35" t="s">
         <v>45</v>
       </c>
-      <c r="I35" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G35">
+        <v>700</v>
+      </c>
+      <c r="J35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B36" t="s">
         <v>73</v>
       </c>
@@ -1333,11 +1443,14 @@
       <c r="F36" t="s">
         <v>48</v>
       </c>
-      <c r="I36" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G36">
+        <v>700</v>
+      </c>
+      <c r="J36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B37" t="s">
         <v>73</v>
       </c>
@@ -1350,11 +1463,14 @@
       <c r="F37" t="s">
         <v>45</v>
       </c>
-      <c r="I37" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G37">
+        <v>700</v>
+      </c>
+      <c r="J37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B38" t="s">
         <v>73</v>
       </c>
@@ -1367,11 +1483,14 @@
       <c r="F38" t="s">
         <v>48</v>
       </c>
-      <c r="I38" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G38">
+        <v>700</v>
+      </c>
+      <c r="J38" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B39" t="s">
         <v>73</v>
       </c>
@@ -1384,11 +1503,14 @@
       <c r="F39" t="s">
         <v>48</v>
       </c>
-      <c r="I39" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G39">
+        <v>700</v>
+      </c>
+      <c r="J39" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
         <v>73</v>
       </c>
@@ -1401,11 +1523,14 @@
       <c r="F40" t="s">
         <v>48</v>
       </c>
-      <c r="I40" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G40">
+        <v>700</v>
+      </c>
+      <c r="J40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B41" t="s">
         <v>73</v>
       </c>
@@ -1418,11 +1543,14 @@
       <c r="F41" t="s">
         <v>45</v>
       </c>
-      <c r="I41" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G41">
+        <v>700</v>
+      </c>
+      <c r="J41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B42" t="s">
         <v>73</v>
       </c>
@@ -1435,11 +1563,14 @@
       <c r="F42" t="s">
         <v>48</v>
       </c>
-      <c r="I42" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G42">
+        <v>700</v>
+      </c>
+      <c r="J42" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B43" t="s">
         <v>73</v>
       </c>
@@ -1452,11 +1583,14 @@
       <c r="F43" t="s">
         <v>45</v>
       </c>
-      <c r="I43" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G43">
+        <v>700</v>
+      </c>
+      <c r="J43" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B44" t="s">
         <v>73</v>
       </c>
@@ -1469,11 +1603,14 @@
       <c r="F44" t="s">
         <v>48</v>
       </c>
-      <c r="I44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G44">
+        <v>700</v>
+      </c>
+      <c r="J44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B45" t="s">
         <v>73</v>
       </c>
@@ -1486,11 +1623,14 @@
       <c r="F45" t="s">
         <v>45</v>
       </c>
-      <c r="I45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G45">
+        <v>700</v>
+      </c>
+      <c r="J45" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B46" t="s">
         <v>88</v>
       </c>
@@ -1503,11 +1643,14 @@
       <c r="F46" t="s">
         <v>42</v>
       </c>
-      <c r="I46" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G46">
+        <v>700</v>
+      </c>
+      <c r="J46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B47" t="s">
         <v>88</v>
       </c>
@@ -1520,11 +1663,14 @@
       <c r="F47" t="s">
         <v>41</v>
       </c>
-      <c r="I47" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G47">
+        <v>700</v>
+      </c>
+      <c r="J47" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B48" t="s">
         <v>88</v>
       </c>
@@ -1537,11 +1683,14 @@
       <c r="F48" t="s">
         <v>43</v>
       </c>
-      <c r="I48" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G48">
+        <v>700</v>
+      </c>
+      <c r="J48" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B49" t="s">
         <v>88</v>
       </c>
@@ -1554,11 +1703,14 @@
       <c r="F49" t="s">
         <v>44</v>
       </c>
-      <c r="I49" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G49">
+        <v>700</v>
+      </c>
+      <c r="J49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B50" t="s">
         <v>88</v>
       </c>
@@ -1571,11 +1723,14 @@
       <c r="F50" t="s">
         <v>42</v>
       </c>
-      <c r="I50" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G50">
+        <v>700</v>
+      </c>
+      <c r="J50" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B51" t="s">
         <v>88</v>
       </c>
@@ -1588,11 +1743,14 @@
       <c r="F51" t="s">
         <v>46</v>
       </c>
-      <c r="I51" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G51">
+        <v>700</v>
+      </c>
+      <c r="J51" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B52" t="s">
         <v>88</v>
       </c>
@@ -1605,11 +1763,14 @@
       <c r="F52" t="s">
         <v>38</v>
       </c>
-      <c r="I52" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G52">
+        <v>700</v>
+      </c>
+      <c r="J52" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B53" t="s">
         <v>88</v>
       </c>
@@ -1622,11 +1783,14 @@
       <c r="F53" t="s">
         <v>39</v>
       </c>
-      <c r="I53" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G53">
+        <v>700</v>
+      </c>
+      <c r="J53" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B54" t="s">
         <v>88</v>
       </c>
@@ -1639,11 +1803,14 @@
       <c r="F54" t="s">
         <v>40</v>
       </c>
-      <c r="I54" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G54">
+        <v>700</v>
+      </c>
+      <c r="J54" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B55" t="s">
         <v>88</v>
       </c>
@@ -1656,11 +1823,14 @@
       <c r="F55" t="s">
         <v>38</v>
       </c>
-      <c r="I55" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="G55">
+        <v>700</v>
+      </c>
+      <c r="J55" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B56" t="s">
         <v>88</v>
       </c>
@@ -1673,7 +1843,10 @@
       <c r="F56" t="s">
         <v>39</v>
       </c>
-      <c r="I56" t="s">
+      <c r="G56">
+        <v>700</v>
+      </c>
+      <c r="J56" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1681,7 +1854,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J1 G2:H2 J2" numberStoredAsText="1"/>
+    <ignoredError sqref="H1:K1 H2:I2 K2 A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>